--- a/technical_logs.xlsx
+++ b/technical_logs.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.5546875" customWidth="1" min="1" max="1"/>
@@ -6101,6 +6101,2466 @@
         <v>97.11</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:21:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="D190" t="n">
+        <v>132.53</v>
+      </c>
+      <c r="E190" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="F190" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="G190" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="H190" t="n">
+        <v>157.95</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:38:51</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="D191" t="n">
+        <v>121.32</v>
+      </c>
+      <c r="E191" t="n">
+        <v>124.34</v>
+      </c>
+      <c r="F191" t="n">
+        <v>46.23</v>
+      </c>
+      <c r="G191" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="H191" t="n">
+        <v>146.29</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:41:12</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="D192" t="n">
+        <v>122.46</v>
+      </c>
+      <c r="E192" t="n">
+        <v>123.21</v>
+      </c>
+      <c r="F192" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="G192" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="H192" t="n">
+        <v>143.29</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:42:11</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>123</v>
+      </c>
+      <c r="D193" t="n">
+        <v>122.62</v>
+      </c>
+      <c r="E193" t="n">
+        <v>122.88</v>
+      </c>
+      <c r="F193" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="G193" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="H193" t="n">
+        <v>142.56</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:55:10</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="D194" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="E194" t="n">
+        <v>112.96</v>
+      </c>
+      <c r="F194" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="G194" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="H194" t="n">
+        <v>108.92</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:55:40</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>NIFTY2620325600CE</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="D195" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="E195" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="F195" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="G195" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="H195" t="n">
+        <v>79.90000000000001</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:56:47</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="D196" t="n">
+        <v>119.03</v>
+      </c>
+      <c r="E196" t="n">
+        <v>113.38</v>
+      </c>
+      <c r="F196" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G196" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="H196" t="n">
+        <v>109.2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:57:15</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>NIFTY2620325200PE</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D197" t="n">
+        <v>125.03</v>
+      </c>
+      <c r="E197" t="n">
+        <v>132.96</v>
+      </c>
+      <c r="F197" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="G197" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="H197" t="n">
+        <v>152.26</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:57:48</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NIFTY2620325200PE</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D198" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="E198" t="n">
+        <v>133.02</v>
+      </c>
+      <c r="F198" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="G198" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="H198" t="n">
+        <v>152.17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:31:39</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>130.58</v>
+      </c>
+      <c r="E199" t="n">
+        <v>133.76</v>
+      </c>
+      <c r="F199" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="G199" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="H199" t="n">
+        <v>130.05</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:33:04</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="D200" t="n">
+        <v>114.84</v>
+      </c>
+      <c r="E200" t="n">
+        <v>116.14</v>
+      </c>
+      <c r="F200" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="G200" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="H200" t="n">
+        <v>111.9</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:34:32</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="D201" t="n">
+        <v>117.89</v>
+      </c>
+      <c r="E201" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="F201" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="G201" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H201" t="n">
+        <v>119.74</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:35:13</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="E202" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="F202" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="G202" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="H202" t="n">
+        <v>104.27</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:35:54</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="D203" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="E203" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="F203" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="G203" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="H203" t="n">
+        <v>119.72</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:36:37</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="D204" t="n">
+        <v>117.89</v>
+      </c>
+      <c r="E204" t="n">
+        <v>116.66</v>
+      </c>
+      <c r="F204" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="G204" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="H204" t="n">
+        <v>119.71</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:39:40</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D205" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="E205" t="n">
+        <v>113.96</v>
+      </c>
+      <c r="F205" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="G205" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="H205" t="n">
+        <v>111.99</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:40:33</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="D206" t="n">
+        <v>116.14</v>
+      </c>
+      <c r="E206" t="n">
+        <v>114.27</v>
+      </c>
+      <c r="F206" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="G206" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="H206" t="n">
+        <v>112.04</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:41:14</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="D207" t="n">
+        <v>116.86</v>
+      </c>
+      <c r="E207" t="n">
+        <v>114.46</v>
+      </c>
+      <c r="F207" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="G207" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="H207" t="n">
+        <v>112.06</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:42:42</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="D208" t="n">
+        <v>131.33</v>
+      </c>
+      <c r="E208" t="n">
+        <v>134.32</v>
+      </c>
+      <c r="F208" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="G208" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="H208" t="n">
+        <v>136.79</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:43:24</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="D209" t="n">
+        <v>135.31</v>
+      </c>
+      <c r="E209" t="n">
+        <v>132.53</v>
+      </c>
+      <c r="F209" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="G209" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="H209" t="n">
+        <v>130.38</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:44:05</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="D210" t="n">
+        <v>130.99</v>
+      </c>
+      <c r="E210" t="n">
+        <v>133.88</v>
+      </c>
+      <c r="F210" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="G210" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="H210" t="n">
+        <v>136.75</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:46:17</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="D211" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="E211" t="n">
+        <v>115.87</v>
+      </c>
+      <c r="F211" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="G211" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="H211" t="n">
+        <v>112.27</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:46:58</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="D212" t="n">
+        <v>135.99</v>
+      </c>
+      <c r="E212" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="F212" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="G212" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="H212" t="n">
+        <v>130.47</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:47:39</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>119.55</v>
+      </c>
+      <c r="D213" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>116.29</v>
+      </c>
+      <c r="F213" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="G213" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="H213" t="n">
+        <v>112.3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:48:20</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>120</v>
+      </c>
+      <c r="D214" t="n">
+        <v>118.38</v>
+      </c>
+      <c r="E214" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="F214" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="G214" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="H214" t="n">
+        <v>112.32</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:49:48</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>129.45</v>
+      </c>
+      <c r="D215" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="E215" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="F215" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="G215" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H215" t="n">
+        <v>136.52</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:50:29</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="D216" t="n">
+        <v>129.63</v>
+      </c>
+      <c r="E216" t="n">
+        <v>130.96</v>
+      </c>
+      <c r="F216" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G216" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="H216" t="n">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:51:56</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="D217" t="n">
+        <v>113.54</v>
+      </c>
+      <c r="E217" t="n">
+        <v>114.19</v>
+      </c>
+      <c r="F217" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G217" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="H217" t="n">
+        <v>119.21</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:52:37</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="D218" t="n">
+        <v>114.24</v>
+      </c>
+      <c r="E218" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="F218" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="G218" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="H218" t="n">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:53:18</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="D219" t="n">
+        <v>134.45</v>
+      </c>
+      <c r="E219" t="n">
+        <v>135</v>
+      </c>
+      <c r="F219" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="G219" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="H219" t="n">
+        <v>130.61</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:54:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>132.45</v>
+      </c>
+      <c r="D220" t="n">
+        <v>131.15</v>
+      </c>
+      <c r="E220" t="n">
+        <v>130.64</v>
+      </c>
+      <c r="F220" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="G220" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="H220" t="n">
+        <v>136.43</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:57:45</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="D221" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="E221" t="n">
+        <v>117.43</v>
+      </c>
+      <c r="F221" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="G221" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H221" t="n">
+        <v>112.52</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:58:27</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="D222" t="n">
+        <v>97.20999999999999</v>
+      </c>
+      <c r="E222" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="F222" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="G222" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H222" t="n">
+        <v>103.6</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:01:29</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="D223" t="n">
+        <v>118.63</v>
+      </c>
+      <c r="E223" t="n">
+        <v>117.61</v>
+      </c>
+      <c r="F223" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="G223" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="H223" t="n">
+        <v>112.61</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:02:55</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D224" t="n">
+        <v>118.56</v>
+      </c>
+      <c r="E224" t="n">
+        <v>117.69</v>
+      </c>
+      <c r="F224" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="G224" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H224" t="n">
+        <v>112.65</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:03:36</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>121.15</v>
+      </c>
+      <c r="D225" t="n">
+        <v>118.98</v>
+      </c>
+      <c r="E225" t="n">
+        <v>117.82</v>
+      </c>
+      <c r="F225" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="G225" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="H225" t="n">
+        <v>112.67</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:04:16</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>125.85</v>
+      </c>
+      <c r="D226" t="n">
+        <v>126.32</v>
+      </c>
+      <c r="E226" t="n">
+        <v>128.01</v>
+      </c>
+      <c r="F226" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="G226" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="H226" t="n">
+        <v>136.1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:05:43</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="D227" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="E227" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="F227" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="G227" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="H227" t="n">
+        <v>136.06</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:06:24</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>131.65</v>
+      </c>
+      <c r="D228" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="E228" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="F228" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="G228" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="H228" t="n">
+        <v>136.04</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:07:05</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="E229" t="n">
+        <v>112</v>
+      </c>
+      <c r="F229" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="G229" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="H229" t="n">
+        <v>118.73</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:07:46</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>104</v>
+      </c>
+      <c r="D230" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="E230" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="F230" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="G230" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H230" t="n">
+        <v>103.34</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:08:27</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="E231" t="n">
+        <v>97.93000000000001</v>
+      </c>
+      <c r="F231" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="G231" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="H231" t="n">
+        <v>103.34</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:09:09</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>138.55</v>
+      </c>
+      <c r="D232" t="n">
+        <v>132.99</v>
+      </c>
+      <c r="E232" t="n">
+        <v>129.84</v>
+      </c>
+      <c r="F232" t="n">
+        <v>66.39</v>
+      </c>
+      <c r="G232" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H232" t="n">
+        <v>136.05</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:09:50</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="D233" t="n">
+        <v>117.08</v>
+      </c>
+      <c r="E233" t="n">
+        <v>113.41</v>
+      </c>
+      <c r="F233" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="G233" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>118.82</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:11:12</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="D234" t="n">
+        <v>106.19</v>
+      </c>
+      <c r="E234" t="n">
+        <v>99.89</v>
+      </c>
+      <c r="F234" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="G234" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="H234" t="n">
+        <v>103.72</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:12:39</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>108.32</v>
+      </c>
+      <c r="E235" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="F235" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="G235" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="H235" t="n">
+        <v>104.01</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:16:19</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="D236" t="n">
+        <v>128</v>
+      </c>
+      <c r="E236" t="n">
+        <v>119.43</v>
+      </c>
+      <c r="F236" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="G236" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="H236" t="n">
+        <v>119.77</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:17:41</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="D237" t="n">
+        <v>124.07</v>
+      </c>
+      <c r="E237" t="n">
+        <v>129.54</v>
+      </c>
+      <c r="F237" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="G237" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="H237" t="n">
+        <v>131.37</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:18:22</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="D238" t="n">
+        <v>112.98</v>
+      </c>
+      <c r="E238" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="F238" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="G238" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="H238" t="n">
+        <v>104.51</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:18:57</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>116.35</v>
+      </c>
+      <c r="D239" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="E239" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="F239" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="G239" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="H239" t="n">
+        <v>104.55</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:19:43</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="D240" t="n">
+        <v>123.71</v>
+      </c>
+      <c r="E240" t="n">
+        <v>128.26</v>
+      </c>
+      <c r="F240" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G240" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="H240" t="n">
+        <v>131.51</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:20:25</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="D241" t="n">
+        <v>123.93</v>
+      </c>
+      <c r="E241" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="F241" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="G241" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="H241" t="n">
+        <v>131.69</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:21:05</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>124.15</v>
+      </c>
+      <c r="D242" t="n">
+        <v>123.81</v>
+      </c>
+      <c r="E242" t="n">
+        <v>126.81</v>
+      </c>
+      <c r="F242" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="G242" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="H242" t="n">
+        <v>131.78</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:21:46</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>117</v>
+      </c>
+      <c r="D243" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="E243" t="n">
+        <v>109.26</v>
+      </c>
+      <c r="F243" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="G243" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="H243" t="n">
+        <v>104.65</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:23:52</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D244" t="n">
+        <v>114.87</v>
+      </c>
+      <c r="E244" t="n">
+        <v>111.22</v>
+      </c>
+      <c r="F244" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="G244" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="H244" t="n">
+        <v>104.54</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:24:28</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>125.55</v>
+      </c>
+      <c r="D245" t="n">
+        <v>123.63</v>
+      </c>
+      <c r="E245" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="F245" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="G245" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="H245" t="n">
+        <v>132.11</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:25:09</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="D246" t="n">
+        <v>124</v>
+      </c>
+      <c r="E246" t="n">
+        <v>124.46</v>
+      </c>
+      <c r="F246" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="G246" t="n">
+        <v>26.23</v>
+      </c>
+      <c r="H246" t="n">
+        <v>132.19</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:25:49</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>NIFTY2620325400CE</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>148.95</v>
+      </c>
+      <c r="D247" t="n">
+        <v>143.45</v>
+      </c>
+      <c r="E247" t="n">
+        <v>143.32</v>
+      </c>
+      <c r="F247" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="G247" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="H247" t="n">
+        <v>151.92</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:26:32</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="D248" t="n">
+        <v>126.06</v>
+      </c>
+      <c r="E248" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F248" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="G248" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="H248" t="n">
+        <v>132.31</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:27:59</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="D249" t="n">
+        <v>126.44</v>
+      </c>
+      <c r="E249" t="n">
+        <v>124.52</v>
+      </c>
+      <c r="F249" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="G249" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H249" t="n">
+        <v>132.34</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:28:45</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>123.95</v>
+      </c>
+      <c r="D250" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="E250" t="n">
+        <v>129.34</v>
+      </c>
+      <c r="F250" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="G250" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="H250" t="n">
+        <v>119.88</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:29:28</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>127</v>
+      </c>
+      <c r="D251" t="n">
+        <v>125.89</v>
+      </c>
+      <c r="E251" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="F251" t="n">
+        <v>52.99</v>
+      </c>
+      <c r="G251" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="H251" t="n">
+        <v>119.76</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:30:52</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="D252" t="n">
+        <v>96.87</v>
+      </c>
+      <c r="E252" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="F252" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="G252" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="H252" t="n">
+        <v>90.15000000000001</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:31:27</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="D253" t="n">
+        <v>112.51</v>
+      </c>
+      <c r="E253" t="n">
+        <v>113.01</v>
+      </c>
+      <c r="F253" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="G253" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H253" t="n">
+        <v>103.72</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:32:03</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="D254" t="n">
+        <v>113.74</v>
+      </c>
+      <c r="E254" t="n">
+        <v>113.27</v>
+      </c>
+      <c r="F254" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="G254" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="H254" t="n">
+        <v>103.73</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:32:38</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="D255" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E255" t="n">
+        <v>113.21</v>
+      </c>
+      <c r="F255" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="G255" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="H255" t="n">
+        <v>103.78</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:33:14</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="D256" t="n">
+        <v>131.04</v>
+      </c>
+      <c r="E256" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="F256" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="G256" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="H256" t="n">
+        <v>119.13</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:33:50</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="D257" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="E257" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="F257" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="G257" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H257" t="n">
+        <v>90.38</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:34:27</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D258" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="E258" t="n">
+        <v>114.08</v>
+      </c>
+      <c r="F258" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="G258" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="H258" t="n">
+        <v>104.29</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:35:03</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="D259" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="E259" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="F259" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="G259" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="H259" t="n">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:35:38</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="D260" t="n">
+        <v>116.93</v>
+      </c>
+      <c r="E260" t="n">
+        <v>114.31</v>
+      </c>
+      <c r="F260" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="G260" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="H260" t="n">
+        <v>104.45</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:36:14</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="D261" t="n">
+        <v>124.04</v>
+      </c>
+      <c r="E261" t="n">
+        <v>124.53</v>
+      </c>
+      <c r="F261" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G261" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H261" t="n">
+        <v>132.92</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:37:41</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="D262" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="E262" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="F262" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="G262" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="H262" t="n">
+        <v>132.82</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:38:21</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>125.95</v>
+      </c>
+      <c r="D263" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="E263" t="n">
+        <v>124.74</v>
+      </c>
+      <c r="F263" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="G263" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="H263" t="n">
+        <v>132.63</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:39:47</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="D264" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="E264" t="n">
+        <v>125.16</v>
+      </c>
+      <c r="F264" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="G264" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="H264" t="n">
+        <v>132.57</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:40:27</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="D265" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="E265" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="F265" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="G265" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="H265" t="n">
+        <v>132.71</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:41:55</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>129.55</v>
+      </c>
+      <c r="D266" t="n">
+        <v>126.95</v>
+      </c>
+      <c r="E266" t="n">
+        <v>125.72</v>
+      </c>
+      <c r="F266" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="G266" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="H266" t="n">
+        <v>132.62</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-01-30 11:42:36</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>127.95</v>
+      </c>
+      <c r="D267" t="n">
+        <v>128.88</v>
+      </c>
+      <c r="E267" t="n">
+        <v>129.61</v>
+      </c>
+      <c r="F267" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G267" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="H267" t="n">
+        <v>120.86</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:08:36</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>NIFTY2620324750PE</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>143.65</v>
+      </c>
+      <c r="D268" t="n">
+        <v>136.54</v>
+      </c>
+      <c r="E268" t="n">
+        <v>120.58</v>
+      </c>
+      <c r="F268" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="G268" t="n">
+        <v>47.12</v>
+      </c>
+      <c r="H268" t="n">
+        <v>116.84</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:09:17</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>NIFTY2620324650PE</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>115</v>
+      </c>
+      <c r="D269" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="E269" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="F269" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="G269" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H269" t="n">
+        <v>81.38</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:12:24</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>NIFTY2620324750CE</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="D270" t="n">
+        <v>119.69</v>
+      </c>
+      <c r="E270" t="n">
+        <v>130.63</v>
+      </c>
+      <c r="F270" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="G270" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="H270" t="n">
+        <v>176.38</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-02-02 11:12:54</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>NIFTY2620324700CE</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="D271" t="n">
+        <v>146.94</v>
+      </c>
+      <c r="E271" t="n">
+        <v>159.02</v>
+      </c>
+      <c r="F271" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="G271" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="H271" t="n">
+        <v>209.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/technical_logs.xlsx
+++ b/technical_logs.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.5546875" customWidth="1" min="1" max="1"/>
@@ -8561,6 +8561,726 @@
         <v>209.1</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:36:41</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="D272" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="E272" t="n">
+        <v>121.51</v>
+      </c>
+      <c r="F272" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="G272" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="H272" t="n">
+        <v>115.91</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:38:27</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="D273" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="E273" t="n">
+        <v>136.96</v>
+      </c>
+      <c r="F273" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="G273" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="H273" t="n">
+        <v>149.42</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:43:38</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="D274" t="n">
+        <v>135.95</v>
+      </c>
+      <c r="E274" t="n">
+        <v>136.77</v>
+      </c>
+      <c r="F274" t="n">
+        <v>51</v>
+      </c>
+      <c r="G274" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="H274" t="n">
+        <v>148.3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:47:09</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D275" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="E275" t="n">
+        <v>120.92</v>
+      </c>
+      <c r="F275" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="G275" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="H275" t="n">
+        <v>115.75</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:50:43</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="D276" t="n">
+        <v>117.41</v>
+      </c>
+      <c r="E276" t="n">
+        <v>120.38</v>
+      </c>
+      <c r="F276" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="G276" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="H276" t="n">
+        <v>115.56</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:59:19</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="D277" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="E277" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="F277" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="G277" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="H277" t="n">
+        <v>115.21</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:04:49</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>115.13</v>
+      </c>
+      <c r="E278" t="n">
+        <v>113.06</v>
+      </c>
+      <c r="F278" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="G278" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="H278" t="n">
+        <v>116.31</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:06:47</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="D279" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="E279" t="n">
+        <v>113.73</v>
+      </c>
+      <c r="F279" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="G279" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="H279" t="n">
+        <v>116.28</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:09:46</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>106</v>
+      </c>
+      <c r="D280" t="n">
+        <v>107.89</v>
+      </c>
+      <c r="E280" t="n">
+        <v>110.69</v>
+      </c>
+      <c r="F280" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="G280" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="H280" t="n">
+        <v>114.58</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:13:00</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="D281" t="n">
+        <v>118.18</v>
+      </c>
+      <c r="E281" t="n">
+        <v>115.98</v>
+      </c>
+      <c r="F281" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="G281" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="H281" t="n">
+        <v>116.32</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:14:34</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>134.65</v>
+      </c>
+      <c r="D282" t="n">
+        <v>135.81</v>
+      </c>
+      <c r="E282" t="n">
+        <v>137.49</v>
+      </c>
+      <c r="F282" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="G282" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H282" t="n">
+        <v>143.06</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:17:21</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600PE</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="D283" t="n">
+        <v>108.36</v>
+      </c>
+      <c r="E283" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="F283" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="G283" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="H283" t="n">
+        <v>113.39</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:19:01</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="D284" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="E284" t="n">
+        <v>149.24</v>
+      </c>
+      <c r="F284" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="G284" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H284" t="n">
+        <v>147.15</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:21:17</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>122.65</v>
+      </c>
+      <c r="D285" t="n">
+        <v>120.47</v>
+      </c>
+      <c r="E285" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="F285" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="G285" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="H285" t="n">
+        <v>116.59</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:25:47</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>123.65</v>
+      </c>
+      <c r="D286" t="n">
+        <v>121.97</v>
+      </c>
+      <c r="E286" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="F286" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="G286" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="H286" t="n">
+        <v>116.66</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:27:39</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600CE</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D287" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="E287" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F287" t="n">
+        <v>76.08</v>
+      </c>
+      <c r="G287" t="n">
+        <v>34.61</v>
+      </c>
+      <c r="H287" t="n">
+        <v>91.54000000000001</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:29:26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="D288" t="n">
+        <v>128.04</v>
+      </c>
+      <c r="E288" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="F288" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="G288" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="H288" t="n">
+        <v>117.8</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:36:54</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="D289" t="n">
+        <v>124.57</v>
+      </c>
+      <c r="E289" t="n">
+        <v>128.23</v>
+      </c>
+      <c r="F289" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G289" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="H289" t="n">
+        <v>137.49</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:39:24</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>125</v>
+      </c>
+      <c r="D290" t="n">
+        <v>124.47</v>
+      </c>
+      <c r="E290" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="F290" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="G290" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="H290" t="n">
+        <v>137.39</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:41:50</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>128</v>
+      </c>
+      <c r="D291" t="n">
+        <v>124.89</v>
+      </c>
+      <c r="E291" t="n">
+        <v>125.66</v>
+      </c>
+      <c r="F291" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="G291" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="H291" t="n">
+        <v>137.3</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:43:42</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="D292" t="n">
+        <v>125.78</v>
+      </c>
+      <c r="E292" t="n">
+        <v>125.15</v>
+      </c>
+      <c r="F292" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G292" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H292" t="n">
+        <v>137.33</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:47:41</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>133.55</v>
+      </c>
+      <c r="D293" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="E293" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="F293" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="G293" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="H293" t="n">
+        <v>118.37</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:50:25</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>132.45</v>
+      </c>
+      <c r="D294" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="E294" t="n">
+        <v>125.66</v>
+      </c>
+      <c r="F294" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="G294" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="H294" t="n">
+        <v>136.47</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:52:06</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="D295" t="n">
+        <v>130.32</v>
+      </c>
+      <c r="E295" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="F295" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="G295" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H295" t="n">
+        <v>136.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/technical_logs.xlsx
+++ b/technical_logs.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.5546875" customWidth="1" min="1" max="1"/>
@@ -9281,6 +9281,96 @@
         <v>136.4</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-03-13 10:53:42</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>NIFTY2631723750CE</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="D296" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="E296" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="F296" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="G296" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="H296" t="n">
+        <v>101.13</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-03-13 10:55:05</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>NIFTY2631723650CE</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="D297" t="n">
+        <v>119.87</v>
+      </c>
+      <c r="E297" t="n">
+        <v>117.23</v>
+      </c>
+      <c r="F297" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="G297" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="H297" t="n">
+        <v>134.24</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-03-13 10:55:42</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="D298" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="E298" t="n">
+        <v>158.03</v>
+      </c>
+      <c r="F298" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="G298" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="H298" t="n">
+        <v>146.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
